--- a/docs/downloads/04/tbl_cm_act_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_cm_act_alaotra_ambatoharanana.xlsx
@@ -384,14 +384,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>12.9</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -402,14 +396,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>3.2</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -420,32 +414,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>77.40000000000001</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -456,14 +450,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C6">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="D6">
-        <v>22.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +468,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="D7">
-        <v>4.1</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +486,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C8">
-        <v>305</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>60.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +511,7 @@
         <v>63</v>
       </c>
       <c r="D9">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10">
@@ -528,14 +522,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
